--- a/outputs/2026-10-03-dummy-datasets/dummy-data-rekap-layanan-kecamatan.xlsx
+++ b/outputs/2026-10-03-dummy-datasets/dummy-data-rekap-layanan-kecamatan.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R81230718659c4a0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panduan" sheetId="2" r:id="R69fd43134a834011"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R8e8ecd87ed09427c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panduan" sheetId="2" r:id="R9d9c6d30ce6d47e8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -73,6 +73,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -215,7 +220,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="48">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -328,8 +333,13 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -3800,7 +3810,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf303c7d244484a6e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc466cc3ff29945b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3857,8 +3867,8 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="38" customHeight="1">
-      <x:c r="A7" s="44" t="str">
-        <x:v>Catatan</x:v>
+      <x:c r="A7" s="43" t="str">
+        <x:v>Tanggal</x:v>
       </x:c>
       <x:c r="B7" s="43" t="str">
         <x:v>2026-03-12</x:v>
@@ -3954,11 +3964,19 @@
       <x:c r="C15" s="43" t="str">
         <x:v>Catatan umum tanpa nama, alamat, nomor kontak, atau isi dokumen.</x:v>
       </x:c>
+    </x:row>
+    <x:row r="17" ht="34" customHeight="1">
+      <x:c r="A17" s="47" t="str">
+        <x:v>Catatan: gunakan data sintetis selama latihan dan jangan memasukkan data pribadi ke ChatGPT.</x:v>
+      </x:c>
+      <x:c r="B17" s="47"/>
+      <x:c r="C17" s="47"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A3:F3"/>
+    <x:mergeCell ref="A17:C17"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
